--- a/ZonasEscolares/excels/CAJAMARCA-JAEN-JAEN.xlsx
+++ b/ZonasEscolares/excels/CAJAMARCA-JAEN-JAEN.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/CAJAMARCA-JAEN-JAEN.xlsx
+++ b/ZonasEscolares/excels/CAJAMARCA-JAEN-JAEN.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,66 +413,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>001</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-5.70668</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-78.80727</v>
-      </c>
-      <c r="I2" t="n">
-        <v>736</v>
-      </c>
-      <c r="J2" t="n">
-        <v>31</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-5.70668</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-78.80727</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>736</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>006</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-5.71465</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-78.8062</v>
-      </c>
-      <c r="I3" t="n">
-        <v>614</v>
-      </c>
-      <c r="J3" t="n">
-        <v>29</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-5.71465</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-78.8062</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>010</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-5.7008</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-78.8112</v>
-      </c>
-      <c r="I4" t="n">
-        <v>395</v>
-      </c>
-      <c r="J4" t="n">
-        <v>17</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-5.7008</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-78.8112</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>011</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-5.7067</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-78.81270000000001</v>
-      </c>
-      <c r="I5" t="n">
-        <v>455</v>
-      </c>
-      <c r="J5" t="n">
-        <v>18</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-5.7067</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-78.8127</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>013</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-5.7075</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-78.8173</v>
-      </c>
-      <c r="I6" t="n">
-        <v>243</v>
-      </c>
-      <c r="J6" t="n">
-        <v>10</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-5.7075</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-78.8173</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>018</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-5.7141</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-78.8109</v>
-      </c>
-      <c r="I7" t="n">
-        <v>214</v>
-      </c>
-      <c r="J7" t="n">
-        <v>9</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-5.7141</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-78.8109</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>019</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-5.715695</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-78.796471</v>
-      </c>
-      <c r="I8" t="n">
-        <v>221</v>
-      </c>
-      <c r="J8" t="n">
-        <v>10</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-5.715695</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-78.796471</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>034</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-5.735607</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-78.79002699999999</v>
-      </c>
-      <c r="I9" t="n">
-        <v>262</v>
-      </c>
-      <c r="J9" t="n">
-        <v>14</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-5.735607</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-78.790027</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>053</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-5.6968</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-78.8085</v>
-      </c>
-      <c r="I10" t="n">
-        <v>261</v>
-      </c>
-      <c r="J10" t="n">
-        <v>10</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-5.6968</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-78.8085</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>17001</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-5.706852</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-78.81146200000001</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1024</v>
-      </c>
-      <c r="J11" t="n">
-        <v>42</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-5.706852</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-78.811462</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>16002</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-5.705158</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-78.813557</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1071</v>
-      </c>
-      <c r="J12" t="n">
-        <v>48</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-5.705158</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-78.813557</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1071</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>16003</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-5.7002</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-78.8125</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1028</v>
-      </c>
-      <c r="J13" t="n">
-        <v>51</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-5.7002</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-78.8125</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1028</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>16004</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-5.7123</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-78.807</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1042</v>
-      </c>
-      <c r="J14" t="n">
-        <v>41</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-5.7123</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-78.807</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1042</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>16005 PEDRO EMILIO PAULET MOSTAJO</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-5.714135</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-78.806462</v>
-      </c>
-      <c r="I15" t="n">
-        <v>730</v>
-      </c>
-      <c r="J15" t="n">
-        <v>32</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-5.714135</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-78.806462</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>16011 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-5.72003438744109</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-78.80147188947571</v>
-      </c>
-      <c r="I16" t="n">
-        <v>925</v>
-      </c>
-      <c r="J16" t="n">
-        <v>47</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-5.72003438744109</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-78.8014718894757</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>16044</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-5.7063</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-78.819</v>
-      </c>
-      <c r="I17" t="n">
-        <v>591</v>
-      </c>
-      <c r="J17" t="n">
-        <v>31</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-5.7063</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-78.819</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>591</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>16049 INMACULADA CONCEPCION</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-5.7151</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-78.79640000000001</v>
-      </c>
-      <c r="I18" t="n">
-        <v>957</v>
-      </c>
-      <c r="J18" t="n">
-        <v>45</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-5.7151</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-78.7964</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>17514</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-5.711251</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-78.80007999999999</v>
-      </c>
-      <c r="I19" t="n">
-        <v>408</v>
-      </c>
-      <c r="J19" t="n">
-        <v>17</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-5.711251</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-78.80008</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>16001 RAMON CASTILLA Y MARQUEZADO</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-5.70673</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-78.80893</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1009</v>
-      </c>
-      <c r="J20" t="n">
-        <v>42</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-5.70673</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-78.80893</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1009</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>16006 CRISTO REY</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-5.7352</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-78.7903</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1373</v>
-      </c>
-      <c r="J21" t="n">
-        <v>69</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-5.7352</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-78.7903</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1373</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>16010 SEÑOR HUAMANTANGA</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-5.835258</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-78.752662</v>
-      </c>
-      <c r="I22" t="n">
-        <v>209</v>
-      </c>
-      <c r="J22" t="n">
-        <v>12</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-5.835258</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-78.752662</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>16036 ALFONSO ARANA VIDAL</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-5.743034</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-78.846557</v>
-      </c>
-      <c r="I23" t="n">
-        <v>205</v>
-      </c>
-      <c r="J23" t="n">
-        <v>18</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-5.743034</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-78.846557</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>16001 RAMON CASTILLA Y MARQUEZADO</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-5.70326</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-78.80670000000001</v>
-      </c>
-      <c r="I24" t="n">
-        <v>781</v>
-      </c>
-      <c r="J24" t="n">
-        <v>44</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-5.70326</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-78.8067</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>781</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>ALFONSO VILLANUEVA PINILLOS</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-5.702602</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-78.80974500000001</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2022</v>
-      </c>
-      <c r="J25" t="n">
-        <v>96</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-5.702602</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-78.809745</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>HERMOGENES MEJIA SOLF</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-5.7044</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-78.809</v>
-      </c>
-      <c r="I26" t="n">
-        <v>246</v>
-      </c>
-      <c r="J26" t="n">
-        <v>14</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-5.7044</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-78.809</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>JAEN DE BRACAMOROS</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-5.70551</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-78.81331400000001</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1218</v>
-      </c>
-      <c r="J27" t="n">
-        <v>78</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-5.70551</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-78.813314</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>VICTOR RAUL HAYA DE LA TORRE</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-5.714702</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-78.802982</v>
-      </c>
-      <c r="I28" t="n">
-        <v>667</v>
-      </c>
-      <c r="J28" t="n">
-        <v>37</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-5.714702</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-78.802982</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>NAZARENO</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-5.70793</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-78.80804000000001</v>
-      </c>
-      <c r="I29" t="n">
-        <v>516</v>
-      </c>
-      <c r="J29" t="n">
-        <v>34</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-5.70793</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-78.80804</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>516</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>ESTEBAN LOPEZ SERVAN</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-5.706543</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-78.807875</v>
-      </c>
-      <c r="I30" t="n">
-        <v>252</v>
-      </c>
-      <c r="J30" t="n">
-        <v>17</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-5.706543</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-78.807875</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>FE Y ALEGRIA 22 SAN LUIS GONZAGA</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-5.714296</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-78.809197</v>
-      </c>
-      <c r="I31" t="n">
-        <v>1327</v>
-      </c>
-      <c r="J31" t="n">
-        <v>71</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-5.714296</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-78.809197</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1327</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>SAGRADO CORAZON</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-5.7091</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-78.8139</v>
-      </c>
-      <c r="I32" t="n">
-        <v>905</v>
-      </c>
-      <c r="J32" t="n">
-        <v>54</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-5.7091</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-78.8139</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>905</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>16081 SEÑOR DE HUAMANTANGA</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-5.7096</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-78.8103</v>
-      </c>
-      <c r="I33" t="n">
-        <v>1300</v>
-      </c>
-      <c r="J33" t="n">
-        <v>65</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-5.7096</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-78.8103</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>APLICACION VICTOR ANDRES BELAUNDE</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-5.70395211134617</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-78.80553322502099</v>
-      </c>
-      <c r="I34" t="n">
-        <v>423</v>
-      </c>
-      <c r="J34" t="n">
-        <v>26</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-5.70395211134617</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-78.805533225021</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>423</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>16673</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-5.526386</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-78.93197000000001</v>
-      </c>
-      <c r="I35" t="n">
-        <v>214</v>
-      </c>
-      <c r="J35" t="n">
-        <v>14</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-5.526386</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-78.93197</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>16024</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-5.612868</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-78.90029699999999</v>
-      </c>
-      <c r="I36" t="n">
-        <v>272</v>
-      </c>
-      <c r="J36" t="n">
-        <v>29</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-5.612868</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-78.900297</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>16040 MARIANO MELGAR</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-5.62342</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-78.85455</v>
-      </c>
-      <c r="I37" t="n">
-        <v>439</v>
-      </c>
-      <c r="J37" t="n">
-        <v>30</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-5.62342</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-78.85455</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>439</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>SAN MARTIN DE TOURS</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-5.932</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-79.22969999999999</v>
-      </c>
-      <c r="I38" t="n">
-        <v>356</v>
-      </c>
-      <c r="J38" t="n">
-        <v>28</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-5.932</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-79.2297</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>051</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-5.6997</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-78.80710000000001</v>
-      </c>
-      <c r="I39" t="n">
-        <v>328</v>
-      </c>
-      <c r="J39" t="n">
-        <v>16</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-5.6997</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-78.8071</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>TALENTUS</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-5.70942</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-78.81008</v>
-      </c>
-      <c r="I40" t="n">
-        <v>434</v>
-      </c>
-      <c r="J40" t="n">
-        <v>17</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-5.70942</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-78.81008</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>092 SOT3. PNP MARINO LINARES JARAMILLO</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-5.7004</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-78.8051</v>
-      </c>
-      <c r="I41" t="n">
-        <v>221</v>
-      </c>
-      <c r="J41" t="n">
-        <v>10</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-5.7004</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-78.8051</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>447</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-5.7191</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-78.8036</v>
-      </c>
-      <c r="I42" t="n">
-        <v>225</v>
-      </c>
-      <c r="J42" t="n">
-        <v>13</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-5.7191</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-78.8036</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>446</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-5.711</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-78.79949999999999</v>
-      </c>
-      <c r="I43" t="n">
-        <v>350</v>
-      </c>
-      <c r="J43" t="n">
-        <v>14</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-5.711</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-78.7995</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>AUGUSTO SALAZAR BONDY</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-5.70615</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-78.80916999999999</v>
-      </c>
-      <c r="I44" t="n">
-        <v>613</v>
-      </c>
-      <c r="J44" t="n">
-        <v>23</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-5.70615</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-78.80917</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>KINDER GARDEN COLLEGE</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-5.70816</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-78.81608</v>
-      </c>
-      <c r="I45" t="n">
-        <v>329</v>
-      </c>
-      <c r="J45" t="n">
-        <v>16</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-5.70816</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-78.81608</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,22 +3237,280 @@
           <t>MONTESSORI SCHOOL</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-5.694349</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-78.79781800000001</v>
-      </c>
-      <c r="I46" t="n">
-        <v>387</v>
-      </c>
-      <c r="J46" t="n">
-        <v>30</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-5.694349</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-78.797818</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>060801</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>121634</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>MI CIELITO</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-5.70147</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-78.8092</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>060801</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>533499</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>LOS HERALDOS</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-5.70369</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-78.80156</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>060801</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>745769</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>JARDIN ECOLOGICO INICIAL</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-5.706981</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-78.816443</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>060801</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>JAEN</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>816323</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1544</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-5.734409</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-78.793647</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/ZonasEscolares/excels/CAJAMARCA-JAEN-JAEN.xlsx
+++ b/ZonasEscolares/excels/CAJAMARCA-JAEN-JAEN.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>119909</t>
+          <t>119947</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>013</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-5.70668</t>
+          <t>-5.7075</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-78.80727</t>
+          <t>-78.8173</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>243</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>119914</t>
+          <t>119966</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>019</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-5.71465</t>
+          <t>-5.715695</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-78.8062</t>
+          <t>-78.796471</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>221</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>119928</t>
+          <t>120088</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>010</t>
+          <t>053</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-5.7008</t>
+          <t>-5.6968</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-78.8112</t>
+          <t>-78.8085</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>261</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>119933</t>
+          <t>538741</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>092 SOT3. PNP MARINO LINARES JARAMILLO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-5.7067</t>
+          <t>-5.7004</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-78.8127</t>
+          <t>-78.8051</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>221</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>119947</t>
+          <t>121163</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>013</t>
+          <t>16010 SEÑOR HUAMANTANGA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-5.7075</t>
+          <t>-5.835258</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-78.8173</t>
+          <t>-78.752662</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>209</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>119952</t>
+          <t>552647</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>018</t>
+          <t>447</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-5.7141</t>
+          <t>-5.7191</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-78.8109</t>
+          <t>-78.8036</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>225</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>119966</t>
+          <t>120031</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>019</t>
+          <t>034</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-5.715695</t>
+          <t>-5.735607</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-78.796471</t>
+          <t>-78.790027</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>262</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,27 +935,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>120031</t>
+          <t>121276</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>034</t>
+          <t>HERMOGENES MEJIA SOLF</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-5.735607</t>
+          <t>-5.7044</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-78.790027</t>
+          <t>-78.809</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>246</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>120088</t>
+          <t>121931</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>053</t>
+          <t>16673</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-5.6968</t>
+          <t>-5.526386</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-78.8085</t>
+          <t>-78.93197</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>214</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>120267</t>
+          <t>587251</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17001</t>
+          <t>446</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-5.706852</t>
+          <t>-5.711</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-78.811462</t>
+          <t>-78.7995</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>350</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>120286</t>
+          <t>506071</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>16002</t>
+          <t>051</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-5.705158</t>
+          <t>-5.6997</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-78.813557</t>
+          <t>-78.8071</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>328</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>120291</t>
+          <t>587524</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>16003</t>
+          <t>KINDER GARDEN COLLEGE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-5.7002</t>
+          <t>-5.70816</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-78.8125</t>
+          <t>-78.81608</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>329</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>120309</t>
+          <t>119928</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>16004</t>
+          <t>010</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-5.7123</t>
+          <t>-5.7008</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-78.807</t>
+          <t>-78.8112</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>395</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>120314</t>
+          <t>121059</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>16005 PEDRO EMILIO PAULET MOSTAJO</t>
+          <t>17514</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-5.714135</t>
+          <t>-5.711251</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-78.806462</t>
+          <t>-78.80008</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>408</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,42 +1369,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>120347</t>
+          <t>121436</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>16011 SEÑOR DE LOS MILAGROS</t>
+          <t>ESTEBAN LOPEZ SERVAN</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-5.72003438744109</t>
+          <t>-5.706543</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-78.8014718894757</t>
+          <t>-78.807875</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>252</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>120502</t>
+          <t>530603</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>16044</t>
+          <t>TALENTUS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-5.7063</t>
+          <t>-5.70942</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-78.819</t>
+          <t>-78.81008</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>434</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>120559</t>
+          <t>119933</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>16049 INMACULADA CONCEPCION</t>
+          <t>011</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-5.7151</t>
+          <t>-5.7067</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-78.7964</t>
+          <t>-78.8127</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>455</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>121059</t>
+          <t>121200</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>17514</t>
+          <t>16036 ALFONSO ARANA VIDAL</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-5.711251</t>
+          <t>-5.743034</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-78.80008</t>
+          <t>-78.846557</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>205</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>121144</t>
+          <t>587312</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>16001 RAMON CASTILLA Y MARQUEZADO</t>
+          <t>AUGUSTO SALAZAR BONDY</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-5.70673</t>
+          <t>-5.70615</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-78.80893</t>
+          <t>-78.80917</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>613</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>121158</t>
+          <t>121610</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>16006 CRISTO REY</t>
+          <t>APLICACION VICTOR ANDRES BELAUNDE</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-5.7352</t>
+          <t>-5.70395211134617</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-78.7903</t>
+          <t>-78.805533225021</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>423</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>121163</t>
+          <t>124185</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>16010 SEÑOR HUAMANTANGA</t>
+          <t>SAN MARTIN DE TOURS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-5.835258</t>
+          <t>-5.932</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-78.752662</t>
+          <t>-79.2297</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>356</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>121200</t>
+          <t>119914</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>16036 ALFONSO ARANA VIDAL</t>
+          <t>006</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-5.743034</t>
+          <t>-5.71465</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-78.846557</t>
+          <t>-78.8062</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>614</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1865,42 +1865,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>121257</t>
+          <t>123671</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>16001 RAMON CASTILLA Y MARQUEZADO</t>
+          <t>16024</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-5.70326</t>
+          <t>-5.612868</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-78.8067</t>
+          <t>-78.900297</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>272</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>121262</t>
+          <t>123954</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ALFONSO VILLANUEVA PINILLOS</t>
+          <t>16040 MARIANO MELGAR</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-5.702602</t>
+          <t>-5.62342</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-78.809745</t>
+          <t>-78.85455</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>439</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>121276</t>
+          <t>718148</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>HERMOGENES MEJIA SOLF</t>
+          <t>MONTESSORI SCHOOL</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-5.7044</t>
+          <t>-5.694349</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-78.809</t>
+          <t>-78.797818</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>387</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>121281</t>
+          <t>119909</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JAEN DE BRACAMOROS</t>
+          <t>001</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-5.70551</t>
+          <t>-5.70668</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-78.813314</t>
+          <t>-78.80727</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>736</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>121304</t>
+          <t>120502</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>VICTOR RAUL HAYA DE LA TORRE</t>
+          <t>16044</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-5.714702</t>
+          <t>-5.7063</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-78.802982</t>
+          <t>-78.819</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>591</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>121399</t>
+          <t>120314</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>NAZARENO</t>
+          <t>16005 PEDRO EMILIO PAULET MOSTAJO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-5.70793</t>
+          <t>-5.714135</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-78.80804</t>
+          <t>-78.806462</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>730</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>121436</t>
+          <t>121399</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ESTEBAN LOPEZ SERVAN</t>
+          <t>NAZARENO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-5.706543</t>
+          <t>-5.70793</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-78.807875</t>
+          <t>-78.80804</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>516</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>121554</t>
+          <t>121304</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 22 SAN LUIS GONZAGA</t>
+          <t>VICTOR RAUL HAYA DE LA TORRE</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-5.714296</t>
+          <t>-5.714702</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-78.809197</t>
+          <t>-78.802982</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>667</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>121592</t>
+          <t>120309</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON</t>
+          <t>16004</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-5.7091</t>
+          <t>-5.7123</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-78.8139</t>
+          <t>-78.807</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>121605</t>
+          <t>120267</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>16081 SEÑOR DE HUAMANTANGA</t>
+          <t>17001</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-5.7096</t>
+          <t>-5.706852</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-78.8103</t>
+          <t>-78.811462</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>121610</t>
+          <t>121144</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>APLICACION VICTOR ANDRES BELAUNDE</t>
+          <t>16001 RAMON CASTILLA Y MARQUEZADO</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-5.70395211134617</t>
+          <t>-5.70673</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-78.805533225021</t>
+          <t>-78.80893</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2547,42 +2547,42 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>121931</t>
+          <t>121257</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>16673</t>
+          <t>16001 RAMON CASTILLA Y MARQUEZADO</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-5.526386</t>
+          <t>-5.70326</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-78.93197</t>
+          <t>-78.8067</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>781</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>123671</t>
+          <t>120559</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>16024</t>
+          <t>16049 INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-5.612868</t>
+          <t>-5.7151</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-78.900297</t>
+          <t>-78.7964</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>957</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2671,42 +2671,42 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>123954</t>
+          <t>120347</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>16040 MARIANO MELGAR</t>
+          <t>16011 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-5.62342</t>
+          <t>-5.72003438744109</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-78.85455</t>
+          <t>-78.8014718894757</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>925</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>124185</t>
+          <t>120286</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SAN MARTIN DE TOURS</t>
+          <t>16002</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-5.932</t>
+          <t>-5.705158</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-79.2297</t>
+          <t>-78.813557</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>506071</t>
+          <t>120291</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>051</t>
+          <t>16003</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-5.6997</t>
+          <t>-5.7002</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-78.8071</t>
+          <t>-78.8125</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>530603</t>
+          <t>121592</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>TALENTUS</t>
+          <t>SAGRADO CORAZON</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-5.70942</t>
+          <t>-5.7091</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-78.81008</t>
+          <t>-78.8139</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>905</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>538741</t>
+          <t>121605</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>092 SOT3. PNP MARINO LINARES JARAMILLO</t>
+          <t>16081 SEÑOR DE HUAMANTANGA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-5.7004</t>
+          <t>-5.7096</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-78.8051</t>
+          <t>-78.8103</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>552647</t>
+          <t>121158</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>16006 CRISTO REY</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-5.7191</t>
+          <t>-5.7352</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-78.8036</t>
+          <t>-78.7903</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>69</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>587251</t>
+          <t>121554</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>FE Y ALEGRIA 22 SAN LUIS GONZAGA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-5.711</t>
+          <t>-5.714296</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-78.7995</t>
+          <t>-78.809197</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>71</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>587312</t>
+          <t>121281</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>AUGUSTO SALAZAR BONDY</t>
+          <t>JAEN DE BRACAMOROS</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-5.70615</t>
+          <t>-5.70551</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-78.80917</t>
+          <t>-78.813314</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>78</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>587524</t>
+          <t>119952</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>KINDER GARDEN COLLEGE</t>
+          <t>018</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-5.70816</t>
+          <t>-5.7141</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-78.81608</t>
+          <t>-78.8109</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>214</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>718148</t>
+          <t>121262</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>MONTESSORI SCHOOL</t>
+          <t>ALFONSO VILLANUEVA PINILLOS</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-5.694349</t>
+          <t>-5.702602</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-78.797818</t>
+          <t>-78.809745</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>96</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">

--- a/ZonasEscolares/excels/CAJAMARCA-JAEN-JAEN.xlsx
+++ b/ZonasEscolares/excels/CAJAMARCA-JAEN-JAEN.xlsx
@@ -821,12 +821,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-5.7191</t>
+          <t>-5.71951813663408</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-78.8036</t>
+          <t>-78.8044783602649</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1441,12 +1441,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-5.70942</t>
+          <t>-5.71255780010051</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-78.81008</t>
+          <t>-78.8234722534834</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -3487,12 +3487,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-5.734409</t>
+          <t>-5.73467751772709</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-78.793647</t>
+          <t>-78.7939993933708</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">

--- a/ZonasEscolares/excels/CAJAMARCA-JAEN-JAEN.xlsx
+++ b/ZonasEscolares/excels/CAJAMARCA-JAEN-JAEN.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>119947</t>
+          <t>816323</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>013</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-5.7075</t>
+          <t>28</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-78.8173</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>-5.73467751772709</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-78.7939993933708</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>119966</t>
+          <t>745769</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>019</t>
+          <t>JARDIN ECOLOGICO INICIAL</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-5.715695</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-78.796471</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>-5.706981</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-78.816443</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>120088</t>
+          <t>718148</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>053</t>
+          <t>MONTESSORI SCHOOL</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-5.6968</t>
+          <t>387</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-78.8085</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>-5.694349</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-78.797818</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>538741</t>
+          <t>587524</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>092 SOT3. PNP MARINO LINARES JARAMILLO</t>
+          <t>KINDER GARDEN COLLEGE</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-5.7004</t>
+          <t>329</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-78.8051</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>-5.70816</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-78.81608</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>121163</t>
+          <t>587312</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>16010 SEÑOR HUAMANTANGA</t>
+          <t>AUGUSTO SALAZAR BONDY</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-5.835258</t>
+          <t>613</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-78.752662</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>-5.70615</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-78.80917</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>552647</t>
+          <t>587251</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>446</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-5.71951813663408</t>
+          <t>350</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-78.8044783602649</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>-5.711</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-78.7995</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>120031</t>
+          <t>552647</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>034</t>
+          <t>447</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-5.735607</t>
+          <t>225</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-78.790027</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>-5.71951813663408</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-78.8044783602649</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>121276</t>
+          <t>538741</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HERMOGENES MEJIA SOLF</t>
+          <t>092 SOT3. PNP MARINO LINARES JARAMILLO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-5.7044</t>
+          <t>221</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-78.809</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>-5.7004</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-78.8051</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>121931</t>
+          <t>533499</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>16673</t>
+          <t>LOS HERALDOS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-5.526386</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-78.93197</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>-5.70369</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-78.80156</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>587251</t>
+          <t>530603</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>TALENTUS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-5.711</t>
+          <t>434</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-78.7995</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>-5.71255780010051</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-78.8234722534834</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1131,22 +1131,22 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>-5.6997</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>-78.8071</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>587524</t>
+          <t>124185</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>KINDER GARDEN COLLEGE</t>
+          <t>SAN MARTIN DE TOURS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-5.70816</t>
+          <t>356</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-78.81608</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>-5.932</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-79.2297</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>119928</t>
+          <t>123954</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>010</t>
+          <t>16040 MARIANO MELGAR</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-5.7008</t>
+          <t>439</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-78.8112</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>-5.62342</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-78.85455</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>121059</t>
+          <t>123671</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>17514</t>
+          <t>16024</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-5.711251</t>
+          <t>272</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-78.80008</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>-5.612868</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-78.900297</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>121436</t>
+          <t>121931</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ESTEBAN LOPEZ SERVAN</t>
+          <t>16673</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-5.706543</t>
+          <t>214</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-78.807875</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>-5.526386</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-78.93197</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>530603</t>
+          <t>121634</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TALENTUS</t>
+          <t>MI CIELITO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-5.71255780010051</t>
+          <t>61</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-78.8234722534834</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>-5.70147</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-78.8092</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>119933</t>
+          <t>121610</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>APLICACION VICTOR ANDRES BELAUNDE</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-5.7067</t>
+          <t>423</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-78.8127</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>-5.70395211134617</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-78.805533225021</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>121200</t>
+          <t>121605</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>16036 ALFONSO ARANA VIDAL</t>
+          <t>16081 SEÑOR DE HUAMANTANGA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-5.743034</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-78.846557</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>-5.7096</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-78.8103</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>587312</t>
+          <t>121592</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AUGUSTO SALAZAR BONDY</t>
+          <t>SAGRADO CORAZON</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-5.70615</t>
+          <t>905</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-78.80917</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>-5.7091</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-78.8139</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>121610</t>
+          <t>121554</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>APLICACION VICTOR ANDRES BELAUNDE</t>
+          <t>FE Y ALEGRIA 22 SAN LUIS GONZAGA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-5.70395211134617</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-78.805533225021</t>
+          <t>71</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>-5.714296</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-78.809197</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>124185</t>
+          <t>121436</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SAN MARTIN DE TOURS</t>
+          <t>ESTEBAN LOPEZ SERVAN</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-5.932</t>
+          <t>252</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-79.2297</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>-5.706543</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-78.807875</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>119914</t>
+          <t>121399</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>006</t>
+          <t>NAZARENO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-5.71465</t>
+          <t>516</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-78.8062</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>-5.70793</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-78.80804</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>123671</t>
+          <t>121304</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>16024</t>
+          <t>VICTOR RAUL HAYA DE LA TORRE</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-5.612868</t>
+          <t>667</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-78.900297</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>-5.714702</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-78.802982</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>123954</t>
+          <t>121281</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>16040 MARIANO MELGAR</t>
+          <t>JAEN DE BRACAMOROS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-5.62342</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-78.85455</t>
+          <t>78</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>-5.70551</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-78.813314</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>718148</t>
+          <t>121276</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MONTESSORI SCHOOL</t>
+          <t>HERMOGENES MEJIA SOLF</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-5.694349</t>
+          <t>246</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-78.797818</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>-5.7044</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-78.809</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>119909</t>
+          <t>121262</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>001</t>
+          <t>ALFONSO VILLANUEVA PINILLOS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-5.70668</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-78.80727</t>
+          <t>96</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>-5.702602</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-78.809745</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2113,42 +2113,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>120502</t>
+          <t>121257</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>16044</t>
+          <t>16001 RAMON CASTILLA Y MARQUEZADO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-5.7063</t>
+          <t>781</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-78.819</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>-5.70326</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-78.8067</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>120314</t>
+          <t>121200</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>16005 PEDRO EMILIO PAULET MOSTAJO</t>
+          <t>16036 ALFONSO ARANA VIDAL</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-5.714135</t>
+          <t>205</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-78.806462</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>-5.743034</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-78.846557</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>121399</t>
+          <t>121163</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>NAZARENO</t>
+          <t>16010 SEÑOR HUAMANTANGA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-5.70793</t>
+          <t>209</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-78.80804</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>-5.835258</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-78.752662</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>121304</t>
+          <t>121158</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>VICTOR RAUL HAYA DE LA TORRE</t>
+          <t>16006 CRISTO REY</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-5.714702</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-78.802982</t>
+          <t>69</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>-5.7352</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-78.7903</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>120309</t>
+          <t>121144</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>16004</t>
+          <t>16001 RAMON CASTILLA Y MARQUEZADO</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-5.7123</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-78.807</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>-5.70673</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-78.80893</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>120267</t>
+          <t>121059</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>17001</t>
+          <t>17514</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-5.706852</t>
+          <t>408</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-78.811462</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>-5.711251</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-78.80008</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>121144</t>
+          <t>120559</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>16001 RAMON CASTILLA Y MARQUEZADO</t>
+          <t>16049 INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-5.70673</t>
+          <t>957</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-78.80893</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>-5.7151</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-78.7964</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2547,42 +2547,42 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>121257</t>
+          <t>120502</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>16001 RAMON CASTILLA Y MARQUEZADO</t>
+          <t>16044</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-5.70326</t>
+          <t>591</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-78.8067</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>-5.7063</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-78.819</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2609,37 +2609,37 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>120559</t>
+          <t>120347</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>16049 INMACULADA CONCEPCION</t>
+          <t>16011 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-5.7151</t>
+          <t>925</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-78.7964</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>-5.72003438744109</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>-78.8014718894757</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2671,37 +2671,37 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>120347</t>
+          <t>120314</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>16011 SEÑOR DE LOS MILAGROS</t>
+          <t>16005 PEDRO EMILIO PAULET MOSTAJO</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-5.72003438744109</t>
+          <t>730</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-78.8014718894757</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>-5.714135</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-78.806462</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>120286</t>
+          <t>120309</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>16002</t>
+          <t>16004</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-5.705158</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-78.813557</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>-5.7123</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-78.807</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2805,22 +2805,22 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
+          <t>1028</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
           <t>-5.7002</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>-78.8125</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1028</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>51</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>121592</t>
+          <t>120286</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SAGRADO CORAZON</t>
+          <t>16002</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-5.7091</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-78.8139</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>-5.705158</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>-78.813557</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>121605</t>
+          <t>120267</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>16081 SEÑOR DE HUAMANTANGA</t>
+          <t>17001</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-5.7096</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-78.8103</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>-5.706852</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>-78.811462</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>121158</t>
+          <t>120088</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>16006 CRISTO REY</t>
+          <t>053</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-5.7352</t>
+          <t>261</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-78.7903</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>-5.6968</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>-78.8085</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>121554</t>
+          <t>120031</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 22 SAN LUIS GONZAGA</t>
+          <t>034</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-5.714296</t>
+          <t>262</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-78.809197</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>-5.735607</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>-78.790027</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>121281</t>
+          <t>119966</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>JAEN DE BRACAMOROS</t>
+          <t>019</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-5.70551</t>
+          <t>221</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-78.813314</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>-5.715695</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>-78.796471</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3177,22 +3177,22 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
           <t>-5.7141</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>-78.8109</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>121262</t>
+          <t>119947</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>ALFONSO VILLANUEVA PINILLOS</t>
+          <t>013</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-5.702602</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-78.809745</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>-5.7075</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>-78.8173</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>121634</t>
+          <t>119933</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MI CIELITO</t>
+          <t>011</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-5.70147</t>
+          <t>455</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-78.8092</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>-5.7067</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-78.8127</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>533499</t>
+          <t>119928</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>LOS HERALDOS</t>
+          <t>010</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-5.70369</t>
+          <t>395</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-78.80156</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-5.7008</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-78.8112</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>745769</t>
+          <t>119914</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>JARDIN ECOLOGICO INICIAL</t>
+          <t>006</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-5.706981</t>
+          <t>614</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-78.816443</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-5.71465</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-78.8062</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>816323</t>
+          <t>119909</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>001</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-5.73467751772709</t>
+          <t>736</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-78.7939993933708</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-5.70668</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-78.80727</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/CAJAMARCA-JAEN-JAEN.xlsx
+++ b/ZonasEscolares/excels/CAJAMARCA-JAEN-JAEN.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
